--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N71_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>77.52570955107491</v>
+        <v>10.11152790452637</v>
       </c>
       <c r="D2" t="n">
-        <v>3.412187094484107</v>
+        <v>3.418477496018904</v>
       </c>
       <c r="E2" t="n">
-        <v>2.776590474362855</v>
+        <v>28.78125480452475</v>
       </c>
       <c r="F2" t="n">
-        <v>21.70636268364587</v>
+        <v>20.30178167953993</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.51337260507526</v>
+        <v>77.52570955107491</v>
       </c>
       <c r="D3" t="n">
-        <v>8.269507471898546</v>
+        <v>3.412187094484107</v>
       </c>
       <c r="E3" t="n">
-        <v>2.776590474362855</v>
+        <v>28.78125480452475</v>
       </c>
       <c r="F3" t="n">
-        <v>21.70636268364587</v>
+        <v>20.30178167953993</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,23 +544,55 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
+        <v>72.51337260507526</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.269507471898546</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28.78125480452475</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20.30178167953993</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T6588</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W0053F0003T0006Z000C1N71.png</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
         <v>79.00073496123082</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>51.69444739655482</v>
       </c>
-      <c r="E4" t="n">
-        <v>2.776590474362855</v>
-      </c>
-      <c r="F4" t="n">
-        <v>21.70636268364587</v>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="E5" t="n">
+        <v>28.78125480452475</v>
+      </c>
+      <c r="F5" t="n">
+        <v>20.30178167953993</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>T6588</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.11152790452637</v>
+        <v>1.643123284485535</v>
       </c>
       <c r="D2" t="n">
-        <v>3.418477496018904</v>
+        <v>0.5555025931030719</v>
       </c>
       <c r="E2" t="n">
-        <v>28.78125480452475</v>
+        <v>4.676953905735273</v>
       </c>
       <c r="F2" t="n">
-        <v>20.30178167953993</v>
+        <v>3.299039522925239</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>77.52570955107491</v>
+        <v>12.59792780204967</v>
       </c>
       <c r="D3" t="n">
-        <v>3.412187094484107</v>
+        <v>0.5544804028536674</v>
       </c>
       <c r="E3" t="n">
-        <v>28.78125480452475</v>
+        <v>4.676953905735273</v>
       </c>
       <c r="F3" t="n">
-        <v>20.30178167953993</v>
+        <v>3.299039522925239</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>72.51337260507526</v>
+        <v>11.78342304832473</v>
       </c>
       <c r="D4" t="n">
-        <v>8.269507471898546</v>
+        <v>1.343794964183514</v>
       </c>
       <c r="E4" t="n">
-        <v>28.78125480452475</v>
+        <v>4.676953905735273</v>
       </c>
       <c r="F4" t="n">
-        <v>20.30178167953993</v>
+        <v>3.299039522925239</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>79.00073496123082</v>
+        <v>12.83761943120001</v>
       </c>
       <c r="D5" t="n">
-        <v>51.69444739655482</v>
+        <v>8.400347701940159</v>
       </c>
       <c r="E5" t="n">
-        <v>28.78125480452475</v>
+        <v>4.676953905735273</v>
       </c>
       <c r="F5" t="n">
-        <v>20.30178167953993</v>
+        <v>3.299039522925239</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
